--- a/outputs/stage_01/nsr10_spectra/data/case_01_nsr10_parameters.xlsx
+++ b/outputs/stage_01/nsr10_spectra/data/case_01_nsr10_parameters.xlsx
@@ -119,7 +119,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>1.25</v>
+        <v>1.0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -199,7 +199,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>1.2578124999999998</v>
+        <v>1.0062499999999999</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
